--- a/Compititor's_Price/Mannok_Prices/Mannok_Prices_24-09-2025.xlsx
+++ b/Compititor's_Price/Mannok_Prices/Mannok_Prices_24-09-2025.xlsx
@@ -483,32 +483,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>£10.45</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>£10.45</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>£10.50</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>£10.50</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>£10.50</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£11.29</t>
         </is>
       </c>
     </row>
@@ -525,12 +525,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£12.30</t>
+          <t>£11.99</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£12.30</t>
+          <t>£11.99</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£12.89</t>
         </is>
       </c>
     </row>
@@ -567,12 +567,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£15.50</t>
+          <t>£15.35</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£15.50</t>
+          <t>£15.35</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£15.45</t>
         </is>
       </c>
     </row>
@@ -609,12 +609,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£15.60</t>
+          <t>£15.45</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£15.60</t>
+          <t>£15.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£16.66</t>
         </is>
       </c>
     </row>
@@ -651,12 +651,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£20.25</t>
+          <t>£19.80</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£20.25</t>
+          <t>£19.80</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£20.99</t>
         </is>
       </c>
     </row>
@@ -693,12 +693,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£22.50</t>
+          <t>£21.75</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£22.50</t>
+          <t>£21.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£22.93</t>
         </is>
       </c>
     </row>
@@ -735,12 +735,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£22.02</t>
+          <t>£22.00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£22.02</t>
+          <t>£22.00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£23.23</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£25.75</t>
+          <t>£25.20</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£25.75</t>
+          <t>£25.20</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£26.86</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£28.00</t>
+          <t>£27.30</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£28.00</t>
+          <t>£27.30</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£28.48</t>
         </is>
       </c>
     </row>
@@ -861,12 +861,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£26.88</t>
+          <t>£26.85</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£26.88</t>
+          <t>£26.85</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£27.89</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£36.00</t>
+          <t>£35.55</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£36.00</t>
+          <t>£35.55</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£34.50</t>
+          <t>£32.95</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£34.50</t>
+          <t>£32.95</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£41.00</t>
+          <t>£40.20</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£41.00</t>
+          <t>£40.20</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£41.50</t>
+          <t>£41.00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£41.50</t>
+          <t>£41.00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£41.66</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£40.95</t>
+          <t>£40.92</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>£40.95</t>
+          <t>£40.92</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
